--- a/docs/Results/statistics.xlsx
+++ b/docs/Results/statistics.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\Documents\Bachelor thesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\PycharmProjects\bachelorThesis\docs\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032E9C16-8FDC-4056-BE17-0BDB4AD18928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A670C32F-25D4-4790-940C-9E78C94A0C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{7C4E5B27-5A65-4098-B759-66245AD6C378}"/>
   </bookViews>
@@ -2911,7 +2911,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -2950,6 +2950,740 @@
               <c:yMode val="edge"/>
               <c:x val="0.11450381679389313"/>
               <c:y val="4.2578150785044087E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2091599695"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE"/>
+              <a:t>MCTS Quality for</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" baseline="0"/>
+              <a:t> Iteration count</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$F$132:$F$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$G$132:$G$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.43</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.239999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41.42</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>87.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>134.06</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>146.55000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>150.36000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>151.53</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>151.77000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>152.79</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>152.78</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>153.16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>153.63999999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>153.47</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>153.77000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D9E2-4FA5-9814-D87F8EE3B081}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>DP algo</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$F$132:$F$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$H$132:$H$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D9E2-4FA5-9814-D87F8EE3B081}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1456379823"/>
+        <c:axId val="1456398063"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1456379823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="20"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Iterations</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.85133202099737526"/>
+              <c:y val="0.87405074365704283"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1456398063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1456398063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE"/>
+                  <a:t>avg. Quality</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="3.0555555555555555E-2"/>
+              <c:y val="8.231846019247592E-2"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -3018,7 +3752,520 @@
             <a:endParaRPr lang="de-DE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2091599695"/>
+        <c:crossAx val="1456379823"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE"/>
+              <a:t>Avg. Charge</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" baseline="0"/>
+              <a:t> through energy harvesting each month</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$F$156:$F$167</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$G$156:$G$167</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>10.97</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.09</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>38.270000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37.409999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>35.43</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>17.04</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.43</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BE41-4C46-9B70-5E5BB21479F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1661476719"/>
+        <c:axId val="1661484879"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1661476719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="12"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Months</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.86745013123359571"/>
+              <c:y val="0.88331000291630213"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1661484879"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1661484879"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Avg. Charge in mAh</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.7777777777777776E-2"/>
+              <c:y val="0.14202938174394864"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1661476719"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3307,6 +4554,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -5888,6 +7215,1038 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6621,6 +8980,78 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Diagramm 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E886230E-7B16-D38B-27C6-D439F98B58C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Diagramm 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BD83D42-BA85-2539-A994-B4070EBCF05F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6941,7 +9372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8730CC4-941E-45DF-A2A6-C299D6C60E13}">
-  <dimension ref="B2:L115"/>
+  <dimension ref="B2:L167"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
@@ -7745,6 +10176,322 @@
       </c>
       <c r="L115">
         <v>5468</v>
+      </c>
+    </row>
+    <row r="132" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="133" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F133">
+        <v>2</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="134" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <v>3</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="135" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <v>4</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="136" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F136">
+        <v>5</v>
+      </c>
+      <c r="G136">
+        <v>4.3</v>
+      </c>
+      <c r="H136">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="137" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F137">
+        <v>6</v>
+      </c>
+      <c r="G137">
+        <v>4.43</v>
+      </c>
+      <c r="H137">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="138" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F138">
+        <v>7</v>
+      </c>
+      <c r="G138">
+        <v>19.239999999999998</v>
+      </c>
+      <c r="H138">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="139" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F139">
+        <v>8</v>
+      </c>
+      <c r="G139">
+        <v>41.42</v>
+      </c>
+      <c r="H139">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="140" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>9</v>
+      </c>
+      <c r="G140">
+        <v>87.3</v>
+      </c>
+      <c r="H140">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="141" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <v>10</v>
+      </c>
+      <c r="G141">
+        <v>134.06</v>
+      </c>
+      <c r="H141">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="142" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <v>11</v>
+      </c>
+      <c r="G142">
+        <v>146.55000000000001</v>
+      </c>
+      <c r="H142">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="143" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F143">
+        <v>12</v>
+      </c>
+      <c r="G143">
+        <v>150.36000000000001</v>
+      </c>
+      <c r="H143">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="144" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <v>13</v>
+      </c>
+      <c r="G144">
+        <v>151.53</v>
+      </c>
+      <c r="H144">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="145" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <v>14</v>
+      </c>
+      <c r="G145">
+        <v>151.77000000000001</v>
+      </c>
+      <c r="H145">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="146" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F146">
+        <v>15</v>
+      </c>
+      <c r="G146">
+        <v>152.79</v>
+      </c>
+      <c r="H146">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="147" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <v>16</v>
+      </c>
+      <c r="G147">
+        <v>152.78</v>
+      </c>
+      <c r="H147">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="148" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F148">
+        <v>17</v>
+      </c>
+      <c r="G148">
+        <v>153.16</v>
+      </c>
+      <c r="H148">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="149" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <v>18</v>
+      </c>
+      <c r="G149">
+        <v>153.63999999999999</v>
+      </c>
+      <c r="H149">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="150" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F150">
+        <v>19</v>
+      </c>
+      <c r="G150">
+        <v>153.47</v>
+      </c>
+      <c r="H150">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="151" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F151">
+        <v>20</v>
+      </c>
+      <c r="G151">
+        <v>153.77000000000001</v>
+      </c>
+      <c r="H151">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="156" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="157" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F157">
+        <v>2</v>
+      </c>
+      <c r="G157">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="158" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F158">
+        <v>3</v>
+      </c>
+      <c r="G158">
+        <v>22.09</v>
+      </c>
+    </row>
+    <row r="159" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F159">
+        <v>4</v>
+      </c>
+      <c r="G159">
+        <v>30.16</v>
+      </c>
+    </row>
+    <row r="160" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F160">
+        <v>5</v>
+      </c>
+      <c r="G160">
+        <v>36.36</v>
+      </c>
+    </row>
+    <row r="161" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F161">
+        <v>6</v>
+      </c>
+      <c r="G161">
+        <v>38.270000000000003</v>
+      </c>
+    </row>
+    <row r="162" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <v>7</v>
+      </c>
+      <c r="G162">
+        <v>37.409999999999997</v>
+      </c>
+    </row>
+    <row r="163" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F163">
+        <v>8</v>
+      </c>
+      <c r="G163">
+        <v>35.43</v>
+      </c>
+    </row>
+    <row r="164" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F164">
+        <v>9</v>
+      </c>
+      <c r="G164">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="165" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F165">
+        <v>10</v>
+      </c>
+      <c r="G165">
+        <v>24.25</v>
+      </c>
+    </row>
+    <row r="166" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F166">
+        <v>11</v>
+      </c>
+      <c r="G166">
+        <v>17.04</v>
+      </c>
+    </row>
+    <row r="167" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F167">
+        <v>12</v>
+      </c>
+      <c r="G167">
+        <v>11.43</v>
       </c>
     </row>
   </sheetData>
